--- a/output/pdf_financials_xlsx/VMXX.xlsx
+++ b/output/pdf_financials_xlsx/VMXX.xlsx
@@ -1207,19 +1207,19 @@
         <v>-0.163864</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.07339</v>
+        <v>-0.07339</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>6.563932</v>
+        <v>-6.563932</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>6.817228</v>
+        <v>-6.817228</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.711078</v>
+        <v>-0.711078</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.6973819999999999</v>
+        <v>-0.6973819999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1475,19 +1475,19 @@
         <v>-0.163864</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.07339</v>
+        <v>-0.07339</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>6.563932</v>
+        <v>-6.563932</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>6.817228</v>
+        <v>-6.817228</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.711078</v>
+        <v>-0.711078</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.6973819999999999</v>
+        <v>-0.6973819999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1631,19 +1631,19 @@
         <v>-0.163864</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.07339</v>
+        <v>-0.07339</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>6.563932</v>
+        <v>-6.563932</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>6.817228</v>
+        <v>-6.817228</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.711078</v>
+        <v>-0.711078</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.6973819999999999</v>
+        <v>-0.6973819999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.112908</v>
+        <v>0.112908</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>-24.310859</v>
+        <v>24.310859</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>-85.21535</v>
+        <v>85.21535</v>
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
@@ -1855,19 +1855,19 @@
         <v>-0.163864</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.07339</v>
+        <v>-0.07339</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>6.563932</v>
+        <v>-6.563932</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>6.817228</v>
+        <v>-6.817228</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.711078</v>
+        <v>-0.711078</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.6973819999999999</v>
+        <v>-0.6973819999999999</v>
       </c>
     </row>
     <row r="28">
@@ -1959,19 +1959,19 @@
         <v>-0.163864</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.07339</v>
+        <v>-0.07339</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>6.563932</v>
+        <v>-6.563932</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>6.817228</v>
+        <v>-6.817228</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.711078</v>
+        <v>-0.711078</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.6973819999999999</v>
+        <v>-0.6973819999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2093,19 +2093,19 @@
         <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5487,34 +5487,34 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.066037</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.066037</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.097162</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.216775</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.263841</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.271605</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.271605</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.271605</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.271605</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.271605</v>
       </c>
       <c r="M92" s="3" t="n">
         <v>0.988446</v>
@@ -11532,7 +11532,11 @@
           <t>Share-based payment reserves</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -12216,7 +12220,11 @@
           <t>Share-based payment reserves</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
           <t>-</t>
@@ -12754,7 +12762,11 @@
           <t>Share-based payment reserves</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -13387,7 +13399,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -24791,10 +24807,10 @@
         </is>
       </c>
       <c r="R191" s="5" t="n">
-        <v>0.711078</v>
+        <v>-0.711078</v>
       </c>
       <c r="S191" s="5" t="n">
-        <v>0.6973819999999999</v>
+        <v>-0.6973819999999999</v>
       </c>
     </row>
     <row r="192">
@@ -24973,10 +24989,10 @@
         </is>
       </c>
       <c r="R193" s="5" t="n">
-        <v>0.807509</v>
+        <v>-0.807509</v>
       </c>
       <c r="S193" s="5" t="n">
-        <v>0.674517</v>
+        <v>-0.674517</v>
       </c>
     </row>
     <row r="194">
@@ -25418,13 +25434,13 @@
         </is>
       </c>
       <c r="P198" s="5" t="n">
-        <v>6.563932</v>
+        <v>-6.563932</v>
       </c>
       <c r="Q198" s="5" t="n">
-        <v>6.817228</v>
+        <v>-6.817228</v>
       </c>
       <c r="R198" s="5" t="n">
-        <v>0.711078</v>
+        <v>-0.711078</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -25598,13 +25614,13 @@
         </is>
       </c>
       <c r="P200" s="5" t="n">
-        <v>6.64771</v>
+        <v>-6.64771</v>
       </c>
       <c r="Q200" s="5" t="n">
-        <v>6.836889</v>
+        <v>-6.836889</v>
       </c>
       <c r="R200" s="5" t="n">
-        <v>0.807509</v>
+        <v>-0.807509</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
@@ -27700,10 +27716,10 @@
         </is>
       </c>
       <c r="O223" s="5" t="n">
-        <v>0.07339</v>
+        <v>-0.07339</v>
       </c>
       <c r="P223" s="5" t="n">
-        <v>6.563932</v>
+        <v>-6.563932</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -27884,10 +27900,10 @@
         </is>
       </c>
       <c r="O225" s="5" t="n">
-        <v>0.07339</v>
+        <v>-0.07339</v>
       </c>
       <c r="P225" s="5" t="n">
-        <v>6.64771</v>
+        <v>-6.64771</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/VMXX.xlsx
+++ b/output/pdf_financials_xlsx/VMXX.xlsx
@@ -1002,16 +1002,16 @@
         <v>0</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.022761</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.172804</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.046434</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.01509</v>
       </c>
     </row>
     <row r="13">
@@ -1858,16 +1858,16 @@
         <v>-0.07339</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-6.563932</v>
+        <v>-6.541171</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-6.817228</v>
+        <v>-6.644424</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.711078</v>
+        <v>-0.664644</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.6973819999999999</v>
+        <v>-0.682292</v>
       </c>
     </row>
     <row r="28">
@@ -1962,16 +1962,16 @@
         <v>-0.07339</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-6.563932</v>
+        <v>-6.541171</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-6.817228</v>
+        <v>-6.644424</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.711078</v>
+        <v>-0.664644</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.6973819999999999</v>
+        <v>-0.682292</v>
       </c>
     </row>
     <row r="30">
@@ -2209,34 +2209,34 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.307</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.267365</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.332657</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.096132</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.09449100000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.113435</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.205565</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.09603399999999999</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.018302</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.261065</v>
       </c>
       <c r="M34" s="3" t="n">
         <v>6.774914</v>
@@ -2317,34 +2317,34 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.307</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.267365</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.332657</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.005</v>
+        <v>0.101132</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.00505</v>
+        <v>0.099541</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.0051</v>
+        <v>0.118535</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.00515</v>
+        <v>0.210715</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.0052</v>
+        <v>0.101234</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.00525</v>
+        <v>0.023552</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.0053</v>
+        <v>0.266365</v>
       </c>
       <c r="M36" s="3" t="n">
         <v>6.780264</v>
@@ -2965,34 +2965,34 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.309165</v>
+        <v>0.002165</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.267365</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.341824</v>
+        <v>0.009167</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.106127</v>
+        <v>0.009995</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.113995</v>
+        <v>0.019504</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.122677</v>
+        <v>0.009242</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.215055</v>
+        <v>0.00949</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.102537</v>
+        <v>0.006503</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.025893</v>
+        <v>0.007591</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.369492</v>
+        <v>0.108427</v>
       </c>
       <c r="M48" s="3" t="n">
         <v>0.279112</v>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -10876,7 +10876,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -24649,7 +24649,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -26918,7 +26918,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">

--- a/output/pdf_financials_xlsx/VMXX.xlsx
+++ b/output/pdf_financials_xlsx/VMXX.xlsx
@@ -7819,7 +7819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S276"/>
+  <dimension ref="A1:S284"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -16487,7 +16487,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E98" t="inlineStr">
         <is>
           <t>-</t>
@@ -23470,7 +23474,11 @@
           <t>Shares issued for cash, net</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>
@@ -23829,29 +23837,31 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Item not involving cash</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Corporate development $</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>Share-based payments</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F181" s="5" t="n">
+        <v>0.059737</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -23903,30 +23913,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q181" s="5" t="n">
-        <v>0.041709</v>
-      </c>
-      <c r="R181" s="5" t="n">
-        <v>0.046528</v>
-      </c>
-      <c r="S181" s="5" t="n">
-        <v>0.021255</v>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Item not involving cash</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses (Notes 5 and 8)</t>
+          <t>Item not involving cash total</t>
         </is>
       </c>
       <c r="D182" t="inlineStr"/>
@@ -23935,10 +23951,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F182" s="5" t="n">
+        <v>-0.053985</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -23995,43 +24009,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="R182" s="5" t="n">
-        <v>0.348958</v>
-      </c>
-      <c r="S182" s="5" t="n">
-        <v>0.377774</v>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Management fees (Note 8)</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>INCREASE IN CASH DURING THE PERIOD</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F183" s="5" t="n">
+        <v>0.307</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -24083,35 +24095,41 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q183" s="5" t="n">
-        <v>0.1482</v>
-      </c>
-      <c r="R183" s="5" t="n">
-        <v>0.14604</v>
-      </c>
-      <c r="S183" s="5" t="n">
-        <v>0.143082</v>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>SUPPLEMENTAL DISCLOSURES</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
+          <t>Interest paid $</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>InterestPaidSupplementalData</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -24169,38 +24187,46 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P184" s="5" t="n">
-        <v>0.029111</v>
-      </c>
-      <c r="Q184" s="5" t="n">
-        <v>0.040065</v>
-      </c>
-      <c r="R184" s="5" t="n">
-        <v>0.029232</v>
-      </c>
-      <c r="S184" s="5" t="n">
-        <v>0.022197</v>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>SUPPLEMENTAL DISCLOSURES</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Professional fees (Note 8)</t>
+          <t>Income taxes paid $</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>IncomeTaxPaidSupplementalData</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -24263,14 +24289,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q185" s="5" t="n">
-        <v>0.12568</v>
-      </c>
-      <c r="R185" s="5" t="n">
-        <v>0.142612</v>
-      </c>
-      <c r="S185" s="5" t="n">
-        <v>0.110597</v>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="186">
@@ -24286,14 +24318,10 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Regulatory and transfer agent</t>
-        </is>
-      </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
+          <t>Corporate development $</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -24349,17 +24377,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P186" s="5" t="n">
-        <v>0.004182</v>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q186" s="5" t="n">
-        <v>0.049102</v>
+        <v>0.041709</v>
       </c>
       <c r="R186" s="5" t="n">
-        <v>0.027679</v>
+        <v>0.046528</v>
       </c>
       <c r="S186" s="5" t="n">
-        <v>0.032736</v>
+        <v>0.021255</v>
       </c>
     </row>
     <row r="187">
@@ -24375,7 +24405,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Camp reclamation provision (Note 6)</t>
+          <t>Exploration and evaluation expenses (Notes 5 and 8)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
@@ -24445,10 +24475,10 @@
         </is>
       </c>
       <c r="R187" s="5" t="n">
-        <v>0.003</v>
+        <v>0.348958</v>
       </c>
       <c r="S187" s="5" t="n">
-        <v>0.003</v>
+        <v>0.377774</v>
       </c>
     </row>
     <row r="188">
@@ -24464,7 +24494,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Shareholder communications and investor relations</t>
+          <t>Management fees (Note 8)</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24533,13 +24563,13 @@
         </is>
       </c>
       <c r="Q188" s="5" t="n">
-        <v>0.062343</v>
+        <v>0.1482</v>
       </c>
       <c r="R188" s="5" t="n">
-        <v>0.013463</v>
+        <v>0.14604</v>
       </c>
       <c r="S188" s="5" t="n">
-        <v>0.001831</v>
+        <v>0.143082</v>
       </c>
     </row>
     <row r="189">
@@ -24555,12 +24585,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Operating loss</t>
+          <t>Office and miscellaneous</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -24619,16 +24649,16 @@
         </is>
       </c>
       <c r="P189" s="5" t="n">
-        <v>6.555846</v>
+        <v>0.029111</v>
       </c>
       <c r="Q189" s="5" t="n">
-        <v>5.386717</v>
+        <v>0.040065</v>
       </c>
       <c r="R189" s="5" t="n">
-        <v>0.757512</v>
+        <v>0.029232</v>
       </c>
       <c r="S189" s="5" t="n">
-        <v>0.712472</v>
+        <v>0.022197</v>
       </c>
     </row>
     <row r="190">
@@ -24644,12 +24674,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Interest Income</t>
+          <t>Professional fees (Note 8)</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -24707,17 +24737,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P190" s="5" t="n">
-        <v>-0.022761</v>
+      <c r="P190" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q190" s="5" t="n">
-        <v>-0.172804</v>
+        <v>0.12568</v>
       </c>
       <c r="R190" s="5" t="n">
-        <v>-0.046434</v>
+        <v>0.142612</v>
       </c>
       <c r="S190" s="5" t="n">
-        <v>-0.01509</v>
+        <v>0.110597</v>
       </c>
     </row>
     <row r="191">
@@ -24733,12 +24765,12 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Loss for the year</t>
+          <t>Regulatory and transfer agent</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -24796,21 +24828,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q191" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P191" s="5" t="n">
+        <v>0.004182</v>
+      </c>
+      <c r="Q191" s="5" t="n">
+        <v>0.049102</v>
       </c>
       <c r="R191" s="5" t="n">
-        <v>-0.711078</v>
+        <v>0.027679</v>
       </c>
       <c r="S191" s="5" t="n">
-        <v>-0.6973819999999999</v>
+        <v>0.032736</v>
       </c>
     </row>
     <row r="192">
@@ -24821,12 +24849,12 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>subsequently to income or loss</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Currency translation differences of foreign operations</t>
+          <t>Camp reclamation provision (Note 6)</t>
         </is>
       </c>
       <c r="D192" t="inlineStr"/>
@@ -24896,10 +24924,10 @@
         </is>
       </c>
       <c r="R192" s="5" t="n">
-        <v>0.096431</v>
+        <v>0.003</v>
       </c>
       <c r="S192" s="5" t="n">
-        <v>-0.022865</v>
+        <v>0.003</v>
       </c>
     </row>
     <row r="193">
@@ -24910,17 +24938,17 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>subsequently to income or loss</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the year $</t>
+          <t>Shareholder communications and investor relations</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -24983,16 +25011,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q193" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q193" s="5" t="n">
+        <v>0.062343</v>
       </c>
       <c r="R193" s="5" t="n">
-        <v>-0.807509</v>
+        <v>0.013463</v>
       </c>
       <c r="S193" s="5" t="n">
-        <v>-0.674517</v>
+        <v>0.001831</v>
       </c>
     </row>
     <row r="194">
@@ -25003,17 +25029,17 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>subsequently to income or loss</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
+          <t>Operating loss</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -25071,21 +25097,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q194" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P194" s="5" t="n">
+        <v>6.555846</v>
+      </c>
+      <c r="Q194" s="5" t="n">
+        <v>5.386717</v>
       </c>
       <c r="R194" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.757512</v>
       </c>
       <c r="S194" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.712472</v>
       </c>
     </row>
     <row r="195">
@@ -25096,15 +25118,19 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Weighted average number of shares</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding (basic and diluted) (Note 9)</t>
-        </is>
-      </c>
-      <c r="D195" t="inlineStr"/>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E195" t="inlineStr">
         <is>
           <t>-</t>
@@ -25160,21 +25186,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q195" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P195" s="5" t="n">
+        <v>-0.022761</v>
+      </c>
+      <c r="Q195" s="5" t="n">
+        <v>-0.172804</v>
       </c>
       <c r="R195" s="5" t="n">
-        <v>83.225336</v>
+        <v>-0.046434</v>
       </c>
       <c r="S195" s="5" t="n">
-        <v>83.225336</v>
+        <v>-0.01509</v>
       </c>
     </row>
     <row r="196">
@@ -25190,10 +25212,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses (Notes 5 ,6 and 8)</t>
-        </is>
-      </c>
-      <c r="D196" t="inlineStr"/>
+          <t>Loss for the year</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E196" t="inlineStr">
         <is>
           <t>-</t>
@@ -25254,16 +25280,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q196" s="5" t="n">
-        <v>4.919618</v>
+      <c r="Q196" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R196" s="5" t="n">
-        <v>0.351958</v>
-      </c>
-      <c r="S196" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.711078</v>
+      </c>
+      <c r="S196" s="5" t="n">
+        <v>-0.6973819999999999</v>
       </c>
     </row>
     <row r="197">
@@ -25274,12 +25300,12 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>subsequently to income or loss</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Impairment of exploration and evaluation assets (Note 5)</t>
+          <t>Currency translation differences of foreign operations</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
@@ -25343,18 +25369,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q197" s="5" t="n">
-        <v>1.603315</v>
-      </c>
-      <c r="R197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S197" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R197" s="5" t="n">
+        <v>0.096431</v>
+      </c>
+      <c r="S197" s="5" t="n">
+        <v>-0.022865</v>
       </c>
     </row>
     <row r="198">
@@ -25365,12 +25389,12 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>subsequently to income or loss</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
+          <t>Total comprehensive loss for the year $</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25433,19 +25457,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P198" s="5" t="n">
-        <v>-6.563932</v>
-      </c>
-      <c r="Q198" s="5" t="n">
-        <v>-6.817228</v>
+      <c r="P198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R198" s="5" t="n">
-        <v>-0.711078</v>
-      </c>
-      <c r="S198" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.807509</v>
+      </c>
+      <c r="S198" s="5" t="n">
+        <v>-0.674517</v>
       </c>
     </row>
     <row r="199">
@@ -25456,15 +25482,19 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>or loss</t>
+          <t>subsequently to income or loss</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Currency translation differences of foreign operations</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr"/>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -25525,16 +25555,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="Q199" s="5" t="n">
-        <v>0.019661</v>
+      <c r="Q199" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R199" s="5" t="n">
-        <v>0.096431</v>
-      </c>
-      <c r="S199" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-08</v>
+      </c>
+      <c r="S199" s="5" t="n">
+        <v>-1e-08</v>
       </c>
     </row>
     <row r="200">
@@ -25545,19 +25575,15 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>or loss</t>
+          <t>Weighted average number of shares</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the year $</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Weighted average number of shares outstanding (basic and diluted) (Note 9)</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr"/>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -25613,19 +25639,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P200" s="5" t="n">
-        <v>-6.64771</v>
-      </c>
-      <c r="Q200" s="5" t="n">
-        <v>-6.836889</v>
+      <c r="P200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R200" s="5" t="n">
-        <v>-0.807509</v>
-      </c>
-      <c r="S200" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>83.225336</v>
+      </c>
+      <c r="S200" s="5" t="n">
+        <v>83.225336</v>
       </c>
     </row>
     <row r="201">
@@ -25636,19 +25664,15 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>or loss</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation expenses (Notes 5 ,6 and 8)</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr"/>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>
@@ -25704,14 +25728,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P201" s="5" t="n">
-        <v>-2.7e-07</v>
+      <c r="P201" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q201" s="5" t="n">
-        <v>-8e-08</v>
+        <v>4.919618</v>
       </c>
       <c r="R201" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.351958</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -25727,12 +25753,12 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Weighted average number of shares outstanding</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>(basic and diluted)</t>
+          <t>Impairment of exploration and evaluation assets (Note 5)</t>
         </is>
       </c>
       <c r="D202" t="inlineStr"/>
@@ -25786,17 +25812,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O202" s="5" t="n">
-        <v>0.112072</v>
-      </c>
-      <c r="P202" s="5" t="n">
-        <v>24.101618</v>
+      <c r="O202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="Q202" s="5" t="n">
-        <v>83.225336</v>
-      </c>
-      <c r="R202" s="5" t="n">
-        <v>83.225336</v>
+        <v>1.603315</v>
+      </c>
+      <c r="R202" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -25817,10 +25849,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses (Notes 6 and 7)</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -25877,15 +25913,13 @@
         </is>
       </c>
       <c r="P203" s="5" t="n">
-        <v>0.150829</v>
+        <v>-6.563932</v>
       </c>
       <c r="Q203" s="5" t="n">
-        <v>4.919618</v>
-      </c>
-      <c r="R203" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.817228</v>
+      </c>
+      <c r="R203" s="5" t="n">
+        <v>-0.711078</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -25901,19 +25935,15 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>or loss</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>ForeignExchangeTradingGains</t>
-        </is>
-      </c>
+          <t>Currency translation differences of foreign operations</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
           <t>-</t>
@@ -25969,18 +25999,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="P204" s="5" t="n">
-        <v>-0.000852</v>
-      </c>
-      <c r="Q204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R204" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q204" s="5" t="n">
+        <v>0.019661</v>
+      </c>
+      <c r="R204" s="5" t="n">
+        <v>0.096431</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
@@ -25996,15 +26024,19 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>or loss</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Gain on debt settlement (Note 8)</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr"/>
+          <t>Total comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E205" t="inlineStr">
         <is>
           <t>-</t>
@@ -26061,17 +26093,13 @@
         </is>
       </c>
       <c r="P205" s="5" t="n">
-        <v>-0.04516</v>
-      </c>
-      <c r="Q205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R205" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-6.64771</v>
+      </c>
+      <c r="Q205" s="5" t="n">
+        <v>-6.836889</v>
+      </c>
+      <c r="R205" s="5" t="n">
+        <v>-0.807509</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
@@ -26087,15 +26115,19 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>or loss</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Listing costs (Note 4)</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr"/>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E206" t="inlineStr">
         <is>
           <t>-</t>
@@ -26152,17 +26184,13 @@
         </is>
       </c>
       <c r="P206" s="5" t="n">
-        <v>5.378548</v>
-      </c>
-      <c r="Q206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R206" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2.7e-07</v>
+      </c>
+      <c r="Q206" s="5" t="n">
+        <v>-8e-08</v>
+      </c>
+      <c r="R206" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -26178,19 +26206,15 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Operating expenses</t>
+          <t>Weighted average number of shares outstanding</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Management fees (Note 9)</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>(basic and diluted)</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -26241,21 +26265,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O207" s="5" t="n">
+        <v>0.112072</v>
       </c>
       <c r="P207" s="5" t="n">
-        <v>0.038692</v>
+        <v>24.101618</v>
       </c>
       <c r="Q207" s="5" t="n">
-        <v>0.1482</v>
-      </c>
-      <c r="R207" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>83.225336</v>
+      </c>
+      <c r="R207" s="5" t="n">
+        <v>83.225336</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -26276,14 +26296,10 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation expenses (Notes 6 and 7)</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
           <t>-</t>
@@ -26340,10 +26356,10 @@
         </is>
       </c>
       <c r="P208" s="5" t="n">
-        <v>0.126774</v>
+        <v>0.150829</v>
       </c>
       <c r="Q208" s="5" t="n">
-        <v>0.12568</v>
+        <v>4.919618</v>
       </c>
       <c r="R208" t="inlineStr">
         <is>
@@ -26369,10 +26385,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Share based compensation (Notes 6 and 9)</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr"/>
+          <t>Foreign exchange</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>ForeignExchangeTradingGains</t>
+        </is>
+      </c>
       <c r="E209" t="inlineStr">
         <is>
           <t>-</t>
@@ -26429,7 +26449,7 @@
         </is>
       </c>
       <c r="P209" s="5" t="n">
-        <v>0.873722</v>
+        <v>-0.000852</v>
       </c>
       <c r="Q209" t="inlineStr">
         <is>
@@ -26460,7 +26480,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Impairment of mineral properties (Note 6)</t>
+          <t>Gain on debt settlement (Note 8)</t>
         </is>
       </c>
       <c r="D210" t="inlineStr"/>
@@ -26520,10 +26540,12 @@
         </is>
       </c>
       <c r="P210" s="5" t="n">
-        <v>0.030846</v>
-      </c>
-      <c r="Q210" s="5" t="n">
-        <v>1.603315</v>
+        <v>-0.04516</v>
+      </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R210" t="inlineStr">
         <is>
@@ -26544,12 +26566,12 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>or loss</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Currency translation adjustments</t>
+          <t>Listing costs (Note 4)</t>
         </is>
       </c>
       <c r="D211" t="inlineStr"/>
@@ -26609,10 +26631,12 @@
         </is>
       </c>
       <c r="P211" s="5" t="n">
-        <v>0.08377800000000001</v>
-      </c>
-      <c r="Q211" s="5" t="n">
-        <v>0.019661</v>
+        <v>5.378548</v>
+      </c>
+      <c r="Q211" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="R211" t="inlineStr">
         <is>
@@ -26633,15 +26657,19 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Exploration and evaluation expenses (Note 6) $</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr"/>
+          <t>Management fees (Note 9)</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E212" t="inlineStr">
         <is>
           <t>-</t>
@@ -26692,16 +26720,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O212" s="5" t="n">
-        <v>0.037405</v>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P212" s="5" t="n">
-        <v>0.150829</v>
-      </c>
-      <c r="Q212" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.038692</v>
+      </c>
+      <c r="Q212" s="5" t="n">
+        <v>0.1482</v>
       </c>
       <c r="R212" t="inlineStr">
         <is>
@@ -26722,17 +26750,17 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Foreign exchange</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>ForeignExchangeTradingGains</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -26791,12 +26819,10 @@
         </is>
       </c>
       <c r="P213" s="5" t="n">
-        <v>-0.000852</v>
-      </c>
-      <c r="Q213" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.126774</v>
+      </c>
+      <c r="Q213" s="5" t="n">
+        <v>0.12568</v>
       </c>
       <c r="R213" t="inlineStr">
         <is>
@@ -26817,12 +26843,12 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Gain on debt settlement (Note 8)</t>
+          <t>Share based compensation (Notes 6 and 9)</t>
         </is>
       </c>
       <c r="D214" t="inlineStr"/>
@@ -26882,7 +26908,7 @@
         </is>
       </c>
       <c r="P214" s="5" t="n">
-        <v>-0.04516</v>
+        <v>0.873722</v>
       </c>
       <c r="Q214" t="inlineStr">
         <is>
@@ -26908,19 +26934,15 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Operating expenses</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
+          <t>Impairment of mineral properties (Note 6)</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr"/>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -26977,12 +26999,10 @@
         </is>
       </c>
       <c r="P215" s="5" t="n">
-        <v>-0.022761</v>
-      </c>
-      <c r="Q215" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.030846</v>
+      </c>
+      <c r="Q215" s="5" t="n">
+        <v>1.603315</v>
       </c>
       <c r="R215" t="inlineStr">
         <is>
@@ -27003,12 +27023,12 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>or loss</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Listing costs (Note 4)</t>
+          <t>Currency translation adjustments</t>
         </is>
       </c>
       <c r="D216" t="inlineStr"/>
@@ -27068,12 +27088,10 @@
         </is>
       </c>
       <c r="P216" s="5" t="n">
-        <v>5.378548</v>
-      </c>
-      <c r="Q216" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.08377800000000001</v>
+      </c>
+      <c r="Q216" s="5" t="n">
+        <v>0.019661</v>
       </c>
       <c r="R216" t="inlineStr">
         <is>
@@ -27099,14 +27117,10 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Management fees (Note 9)</t>
-        </is>
-      </c>
-      <c r="D217" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation expenses (Note 6) $</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr"/>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -27157,13 +27171,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O217" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O217" s="5" t="n">
+        <v>0.037405</v>
       </c>
       <c r="P217" s="5" t="n">
-        <v>0.038692</v>
+        <v>0.150829</v>
       </c>
       <c r="Q217" t="inlineStr">
         <is>
@@ -27194,12 +27206,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Office and miscellaneous</t>
+          <t>Foreign exchange</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ForeignExchangeTradingGains</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -27252,11 +27264,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O218" s="5" t="n">
-        <v>0.000632</v>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P218" s="5" t="n">
-        <v>0.029111</v>
+        <v>-0.000852</v>
       </c>
       <c r="Q218" t="inlineStr">
         <is>
@@ -27287,14 +27301,10 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D219" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
+          <t>Gain on debt settlement (Note 8)</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr"/>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -27345,11 +27355,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O219" s="5" t="n">
-        <v>0.035353</v>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P219" s="5" t="n">
-        <v>0.126774</v>
+        <v>-0.04516</v>
       </c>
       <c r="Q219" t="inlineStr">
         <is>
@@ -27380,12 +27392,12 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Regulatory and transfer agent</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
@@ -27444,7 +27456,7 @@
         </is>
       </c>
       <c r="P220" s="5" t="n">
-        <v>0.004182</v>
+        <v>-0.022761</v>
       </c>
       <c r="Q220" t="inlineStr">
         <is>
@@ -27475,7 +27487,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Stock based compensation (Notes 6, 9)</t>
+          <t>Listing costs (Note 4)</t>
         </is>
       </c>
       <c r="D221" t="inlineStr"/>
@@ -27535,7 +27547,7 @@
         </is>
       </c>
       <c r="P221" s="5" t="n">
-        <v>0.873722</v>
+        <v>5.378548</v>
       </c>
       <c r="Q221" t="inlineStr">
         <is>
@@ -27566,10 +27578,14 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Write off mineral properties (Note 6)</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr"/>
+          <t>Management fees (Note 9)</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -27626,7 +27642,7 @@
         </is>
       </c>
       <c r="P222" s="5" t="n">
-        <v>0.030846</v>
+        <v>0.038692</v>
       </c>
       <c r="Q222" t="inlineStr">
         <is>
@@ -27657,12 +27673,12 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Net loss for the year</t>
+          <t>Office and miscellaneous</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -27716,10 +27732,10 @@
         </is>
       </c>
       <c r="O223" s="5" t="n">
-        <v>-0.07339</v>
+        <v>0.000632</v>
       </c>
       <c r="P223" s="5" t="n">
-        <v>-6.563932</v>
+        <v>0.029111</v>
       </c>
       <c r="Q223" t="inlineStr">
         <is>
@@ -27745,15 +27761,19 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>income or loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Currency translation differences of foreign operations</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr"/>
+          <t>Professional fees</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
       <c r="E224" t="inlineStr">
         <is>
           <t>-</t>
@@ -27804,13 +27824,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O224" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O224" s="5" t="n">
+        <v>0.035353</v>
       </c>
       <c r="P224" s="5" t="n">
-        <v>0.08377800000000001</v>
+        <v>0.126774</v>
       </c>
       <c r="Q224" t="inlineStr">
         <is>
@@ -27836,17 +27854,17 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>income or loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Total comprehensive loss for the year $</t>
+          <t>Regulatory and transfer agent</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherOperatingExpenses</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -27899,11 +27917,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O225" s="5" t="n">
-        <v>-0.07339</v>
+      <c r="O225" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P225" s="5" t="n">
-        <v>-6.64771</v>
+        <v>0.004182</v>
       </c>
       <c r="Q225" t="inlineStr">
         <is>
@@ -27929,19 +27949,15 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>income or loss</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per share $</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Stock based compensation (Notes 6, 9)</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr"/>
       <c r="E226" t="inlineStr">
         <is>
           <t>-</t>
@@ -27992,11 +28008,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O226" s="5" t="n">
-        <v>-6.5e-07</v>
+      <c r="O226" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P226" s="5" t="n">
-        <v>-2.7e-07</v>
+        <v>0.873722</v>
       </c>
       <c r="Q226" t="inlineStr">
         <is>
@@ -28022,12 +28040,12 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Exploration expenditures (Note 5) $</t>
+          <t>Write off mineral properties (Note 6)</t>
         </is>
       </c>
       <c r="D227" t="inlineStr"/>
@@ -28087,7 +28105,7 @@
         </is>
       </c>
       <c r="P227" s="5" t="n">
-        <v>0.036472</v>
+        <v>0.030846</v>
       </c>
       <c r="Q227" t="inlineStr">
         <is>
@@ -28113,15 +28131,19 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Expenses</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Transaction costs</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>Net loss for the year</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
           <t>-</t>
@@ -28172,13 +28194,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="O228" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="O228" s="5" t="n">
+        <v>-0.07339</v>
       </c>
       <c r="P228" s="5" t="n">
-        <v>0.444816</v>
+        <v>-6.563932</v>
       </c>
       <c r="Q228" t="inlineStr">
         <is>
@@ -28204,19 +28224,15 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>income or loss</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Management fees (Note 8)</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Currency translation differences of foreign operations</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr"/>
       <c r="E229" t="inlineStr">
         <is>
           <t>-</t>
@@ -28262,14 +28278,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N229" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="O229" s="5" t="n">
-        <v>0.06</v>
+      <c r="N229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O229" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P229" s="5" t="n">
-        <v>0.06</v>
+        <v>0.08377800000000001</v>
       </c>
       <c r="Q229" t="inlineStr">
         <is>
@@ -28295,50 +28315,74 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>income or loss</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Office, administration and miscellaneous</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr"/>
-      <c r="E230" s="5" t="n">
-        <v>0.009615</v>
-      </c>
-      <c r="F230" s="5" t="n">
-        <v>0.007279</v>
-      </c>
-      <c r="G230" s="5" t="n">
-        <v>0.009615</v>
-      </c>
-      <c r="H230" s="5" t="n">
-        <v>0.051606</v>
-      </c>
-      <c r="I230" s="5" t="n">
-        <v>0.09625499999999999</v>
-      </c>
-      <c r="J230" s="5" t="n">
-        <v>0.03712</v>
-      </c>
-      <c r="K230" s="5" t="n">
-        <v>0.087216</v>
-      </c>
-      <c r="L230" s="5" t="n">
-        <v>0.02246</v>
-      </c>
-      <c r="M230" s="5" t="n">
-        <v>0.019517</v>
-      </c>
-      <c r="N230" s="5" t="n">
-        <v>0.017788</v>
+          <t>Total comprehensive loss for the year $</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N230" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O230" s="5" t="n">
-        <v>0.02582</v>
+        <v>-0.07339</v>
       </c>
       <c r="P230" s="5" t="n">
-        <v>0.0332</v>
+        <v>-6.64771</v>
       </c>
       <c r="Q230" t="inlineStr">
         <is>
@@ -28364,15 +28408,19 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>income or loss</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Other</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr"/>
+          <t>Basic and diluted loss per share $</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>
@@ -28418,14 +28466,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N231" s="5" t="n">
-        <v>0.000423</v>
+      <c r="N231" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O231" s="5" t="n">
-        <v>0.000468</v>
+        <v>-6.5e-07</v>
       </c>
       <c r="P231" s="5" t="n">
-        <v>-0.000687</v>
+        <v>-2.7e-07</v>
       </c>
       <c r="Q231" t="inlineStr">
         <is>
@@ -28456,14 +28506,10 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Professional and consulting fees (Note 8)</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exploration expenditures (Note 5) $</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr"/>
       <c r="E232" t="inlineStr">
         <is>
           <t>-</t>
@@ -28504,17 +28550,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M232" s="5" t="n">
-        <v>0.047977</v>
-      </c>
-      <c r="N232" s="5" t="n">
-        <v>0.039386</v>
-      </c>
-      <c r="O232" s="5" t="n">
-        <v>0.033791</v>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O232" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P232" s="5" t="n">
-        <v>0.047479</v>
+        <v>0.036472</v>
       </c>
       <c r="Q232" t="inlineStr">
         <is>
@@ -28545,7 +28597,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Property investigation</t>
+          <t>Transaction costs</t>
         </is>
       </c>
       <c r="D233" t="inlineStr"/>
@@ -28605,7 +28657,7 @@
         </is>
       </c>
       <c r="P233" s="5" t="n">
-        <v>0.01986</v>
+        <v>0.444816</v>
       </c>
       <c r="Q233" t="inlineStr">
         <is>
@@ -28636,7 +28688,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Regulatory and transfer agent fees</t>
+          <t>Management fees (Note 8)</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -28644,41 +28696,59 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E234" s="5" t="n">
-        <v>0.013846</v>
-      </c>
-      <c r="F234" s="5" t="n">
-        <v>0.025418</v>
-      </c>
-      <c r="G234" s="5" t="n">
-        <v>0.013846</v>
-      </c>
-      <c r="H234" s="5" t="n">
-        <v>0.028804</v>
-      </c>
-      <c r="I234" s="5" t="n">
-        <v>0.024244</v>
-      </c>
-      <c r="J234" s="5" t="n">
-        <v>0.01795</v>
-      </c>
-      <c r="K234" s="5" t="n">
-        <v>0.018395</v>
-      </c>
-      <c r="L234" s="5" t="n">
-        <v>0.018257</v>
-      </c>
-      <c r="M234" s="5" t="n">
-        <v>0.011604</v>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N234" s="5" t="n">
-        <v>0.014037</v>
+        <v>0.06</v>
       </c>
       <c r="O234" s="5" t="n">
-        <v>0.01489</v>
+        <v>0.06</v>
       </c>
       <c r="P234" s="5" t="n">
-        <v>0.027169</v>
+        <v>0.06</v>
       </c>
       <c r="Q234" t="inlineStr">
         <is>
@@ -28709,65 +28779,45 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>LOSS FROM OPERATIONS BEFORE OTHER ITEMS</t>
+          <t>Office, administration and miscellaneous</t>
         </is>
       </c>
       <c r="D235" t="inlineStr"/>
-      <c r="E235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N235" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E235" s="5" t="n">
+        <v>0.009615</v>
+      </c>
+      <c r="F235" s="5" t="n">
+        <v>0.007279</v>
+      </c>
+      <c r="G235" s="5" t="n">
+        <v>0.009615</v>
+      </c>
+      <c r="H235" s="5" t="n">
+        <v>0.051606</v>
+      </c>
+      <c r="I235" s="5" t="n">
+        <v>0.09625499999999999</v>
+      </c>
+      <c r="J235" s="5" t="n">
+        <v>0.03712</v>
+      </c>
+      <c r="K235" s="5" t="n">
+        <v>0.087216</v>
+      </c>
+      <c r="L235" s="5" t="n">
+        <v>0.02246</v>
+      </c>
+      <c r="M235" s="5" t="n">
+        <v>0.019517</v>
+      </c>
+      <c r="N235" s="5" t="n">
+        <v>0.017788</v>
       </c>
       <c r="O235" s="5" t="n">
-        <v>-0.134969</v>
+        <v>0.02582</v>
       </c>
       <c r="P235" s="5" t="n">
-        <v>-0.668309</v>
+        <v>0.0332</v>
       </c>
       <c r="Q235" t="inlineStr">
         <is>
@@ -28798,14 +28848,10 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Other income</t>
-        </is>
-      </c>
-      <c r="D236" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr"/>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -28851,18 +28897,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O236" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N236" s="5" t="n">
+        <v>0.000423</v>
+      </c>
+      <c r="O236" s="5" t="n">
+        <v>0.000468</v>
       </c>
       <c r="P236" s="5" t="n">
-        <v>0.019153</v>
+        <v>-0.000687</v>
       </c>
       <c r="Q236" t="inlineStr">
         <is>
@@ -28893,12 +28935,12 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>NET AND COMPREHENSIVE LOSS FOR THE YEAR $</t>
+          <t>Professional and consulting fees (Note 8)</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
@@ -28942,16 +28984,16 @@
         </is>
       </c>
       <c r="M237" s="5" t="n">
-        <v>-0.195726</v>
+        <v>0.047977</v>
       </c>
       <c r="N237" s="5" t="n">
-        <v>-0.163864</v>
+        <v>0.039386</v>
       </c>
       <c r="O237" s="5" t="n">
-        <v>-0.134969</v>
+        <v>0.033791</v>
       </c>
       <c r="P237" s="5" t="n">
-        <v>-0.649156</v>
+        <v>0.047479</v>
       </c>
       <c r="Q237" t="inlineStr">
         <is>
@@ -28982,14 +29024,10 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>LOSS PER SHARE – BASIC AND DILUTED (NOTE 12) $</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Property investigation</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
@@ -29030,17 +29068,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M238" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N238" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="O238" s="5" t="n">
-        <v>0</v>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O238" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P238" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.01986</v>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
@@ -29066,50 +29110,54 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>OUTSTANDING</t>
-        </is>
-      </c>
-      <c r="D239" t="inlineStr"/>
+          <t>Regulatory and transfer agent fees</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E239" s="5" t="n">
-        <v>6.325</v>
+        <v>0.013846</v>
       </c>
       <c r="F239" s="5" t="n">
-        <v>4.654108</v>
+        <v>0.025418</v>
       </c>
       <c r="G239" s="5" t="n">
-        <v>25.3</v>
+        <v>0.013846</v>
       </c>
       <c r="H239" s="5" t="n">
-        <v>27.256055</v>
+        <v>0.028804</v>
       </c>
       <c r="I239" s="5" t="n">
-        <v>36.778423</v>
+        <v>0.024244</v>
       </c>
       <c r="J239" s="5" t="n">
-        <v>40.611907</v>
+        <v>0.01795</v>
       </c>
       <c r="K239" s="5" t="n">
-        <v>48.375764</v>
+        <v>0.018395</v>
       </c>
       <c r="L239" s="5" t="n">
-        <v>51.735</v>
+        <v>0.018257</v>
       </c>
       <c r="M239" s="5" t="n">
-        <v>55.731865</v>
+        <v>0.011604</v>
       </c>
       <c r="N239" s="5" t="n">
-        <v>55.731865</v>
+        <v>0.014037</v>
       </c>
       <c r="O239" s="5" t="n">
-        <v>58.910158</v>
+        <v>0.01489</v>
       </c>
       <c r="P239" s="5" t="n">
-        <v>62.398974</v>
+        <v>0.027169</v>
       </c>
       <c r="Q239" t="inlineStr">
         <is>
@@ -29140,7 +29188,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Exploration and evaluation costs (Note 5) $</t>
+          <t>LOSS FROM OPERATIONS BEFORE OTHER ITEMS</t>
         </is>
       </c>
       <c r="D240" t="inlineStr"/>
@@ -29189,18 +29237,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N240" s="5" t="n">
-        <v>0.03223</v>
-      </c>
-      <c r="O240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P240" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N240" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O240" s="5" t="n">
+        <v>-0.134969</v>
+      </c>
+      <c r="P240" s="5" t="n">
+        <v>-0.668309</v>
       </c>
       <c r="Q240" t="inlineStr">
         <is>
@@ -29231,12 +29277,12 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Management fees (Note 8) $</t>
+          <t>Other income</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -29279,21 +29325,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="M241" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="N241" s="5" t="n">
-        <v>0.06</v>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N241" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="O241" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="P241" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="P241" s="5" t="n">
+        <v>0.019153</v>
       </c>
       <c r="Q241" t="inlineStr">
         <is>
@@ -29324,10 +29372,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Exploration and evaluation costs (Note 5)</t>
-        </is>
-      </c>
-      <c r="D242" t="inlineStr"/>
+          <t>NET AND COMPREHENSIVE LOSS FOR THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E242" t="inlineStr">
         <is>
           <t>-</t>
@@ -29369,20 +29421,16 @@
         </is>
       </c>
       <c r="M242" s="5" t="n">
-        <v>0.03503</v>
+        <v>-0.195726</v>
       </c>
       <c r="N242" s="5" t="n">
-        <v>0.03223</v>
-      </c>
-      <c r="O242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P242" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.163864</v>
+      </c>
+      <c r="O242" s="5" t="n">
+        <v>-0.134969</v>
+      </c>
+      <c r="P242" s="5" t="n">
+        <v>-0.649156</v>
       </c>
       <c r="Q242" t="inlineStr">
         <is>
@@ -29413,10 +29461,14 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Property investigation costs</t>
-        </is>
-      </c>
-      <c r="D243" t="inlineStr"/>
+          <t>LOSS PER SHARE – BASIC AND DILUTED (NOTE 12) $</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
@@ -29447,8 +29499,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="K243" s="5" t="n">
-        <v>0.173911</v>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
@@ -29456,22 +29510,16 @@
         </is>
       </c>
       <c r="M243" s="5" t="n">
-        <v>0.020002</v>
-      </c>
-      <c r="N243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P243" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="N243" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P243" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="Q243" t="inlineStr">
         <is>
@@ -29497,70 +29545,50 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Foreign exchange (gain) loss</t>
-        </is>
-      </c>
-      <c r="D244" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OUTSTANDING</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" s="5" t="n">
+        <v>6.325</v>
+      </c>
+      <c r="F244" s="5" t="n">
+        <v>4.654108</v>
+      </c>
+      <c r="G244" s="5" t="n">
+        <v>25.3</v>
+      </c>
+      <c r="H244" s="5" t="n">
+        <v>27.256055</v>
+      </c>
+      <c r="I244" s="5" t="n">
+        <v>36.778423</v>
+      </c>
+      <c r="J244" s="5" t="n">
+        <v>40.611907</v>
       </c>
       <c r="K244" s="5" t="n">
-        <v>0.000363</v>
+        <v>48.375764</v>
       </c>
       <c r="L244" s="5" t="n">
-        <v>-0.002108</v>
+        <v>51.735</v>
       </c>
       <c r="M244" s="5" t="n">
-        <v>0.001109</v>
+        <v>55.731865</v>
       </c>
       <c r="N244" s="5" t="n">
-        <v>-4.5e-05</v>
-      </c>
-      <c r="O244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P244" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>55.731865</v>
+      </c>
+      <c r="O244" s="5" t="n">
+        <v>58.910158</v>
+      </c>
+      <c r="P244" s="5" t="n">
+        <v>62.398974</v>
       </c>
       <c r="Q244" t="inlineStr">
         <is>
@@ -29591,14 +29619,10 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Interest and bank charges</t>
-        </is>
-      </c>
-      <c r="D245" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation costs (Note 5) $</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr"/>
       <c r="E245" t="inlineStr">
         <is>
           <t>-</t>
@@ -29609,29 +29633,43 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G245" s="5" t="n">
-        <v>3.6e-05</v>
-      </c>
-      <c r="H245" s="5" t="n">
-        <v>5.2e-05</v>
-      </c>
-      <c r="I245" s="5" t="n">
-        <v>0.000367</v>
-      </c>
-      <c r="J245" s="5" t="n">
-        <v>0.000368</v>
-      </c>
-      <c r="K245" s="5" t="n">
-        <v>0.000816</v>
-      </c>
-      <c r="L245" s="5" t="n">
-        <v>0.0005</v>
-      </c>
-      <c r="M245" s="5" t="n">
-        <v>0.000487</v>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="N245" s="5" t="n">
-        <v>0.000468</v>
+        <v>0.03223</v>
       </c>
       <c r="O245" t="inlineStr">
         <is>
@@ -29672,7 +29710,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Management fees (Note 9) $</t>
+          <t>Management fees (Note 8) $</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -29695,30 +29733,36 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H246" s="5" t="n">
-        <v>0.166613</v>
-      </c>
-      <c r="I246" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J246" s="5" t="n">
-        <v>0.06</v>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K246" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L246" s="5" t="n">
-        <v>0.06</v>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M246" s="5" t="n">
         <v>0.06</v>
       </c>
-      <c r="N246" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="N246" s="5" t="n">
+        <v>0.06</v>
       </c>
       <c r="O246" t="inlineStr">
         <is>
@@ -29759,14 +29803,10 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Professional and consulting fees (Note 9)</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation costs (Note 5)</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr"/>
       <c r="E247" t="inlineStr">
         <is>
           <t>-</t>
@@ -29787,25 +29827,31 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I247" s="5" t="n">
-        <v>0.176791</v>
-      </c>
-      <c r="J247" s="5" t="n">
-        <v>0.056886</v>
-      </c>
-      <c r="K247" s="5" t="n">
-        <v>0.09901699999999999</v>
-      </c>
-      <c r="L247" s="5" t="n">
-        <v>0.077676</v>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M247" s="5" t="n">
-        <v>0.047977</v>
-      </c>
-      <c r="N247" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.03503</v>
+      </c>
+      <c r="N247" s="5" t="n">
+        <v>0.03223</v>
       </c>
       <c r="O247" t="inlineStr">
         <is>
@@ -29846,7 +29892,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Exploration and evaluation costs (Note 6)</t>
+          <t>Property investigation costs</t>
         </is>
       </c>
       <c r="D248" t="inlineStr"/>
@@ -29870,20 +29916,26 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I248" s="5" t="n">
-        <v>0.335639</v>
-      </c>
-      <c r="J248" s="5" t="n">
-        <v>-0.000106</v>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K248" s="5" t="n">
-        <v>0.0277</v>
-      </c>
-      <c r="L248" s="5" t="n">
-        <v>0.018954</v>
+        <v>0.173911</v>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="M248" s="5" t="n">
-        <v>0.03503</v>
+        <v>0.020002</v>
       </c>
       <c r="N248" t="inlineStr">
         <is>
@@ -29929,12 +29981,12 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>LOSS FROM OPERATIONS</t>
+          <t>Foreign exchange (gain) loss</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -29962,22 +30014,22 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J249" s="5" t="n">
-        <v>-0.219747</v>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="K249" s="5" t="n">
-        <v>-0.475182</v>
+        <v>0.000363</v>
       </c>
       <c r="L249" s="5" t="n">
-        <v>-0.195739</v>
+        <v>-0.002108</v>
       </c>
       <c r="M249" s="5" t="n">
-        <v>-0.195726</v>
-      </c>
-      <c r="N249" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.001109</v>
+      </c>
+      <c r="N249" s="5" t="n">
+        <v>-4.5e-05</v>
       </c>
       <c r="O249" t="inlineStr">
         <is>
@@ -30013,15 +30065,19 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Loss on debt settlement (Note 7)</t>
-        </is>
-      </c>
-      <c r="D250" t="inlineStr"/>
+          <t>Interest and bank charges</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E250" t="inlineStr">
         <is>
           <t>-</t>
@@ -30032,43 +30088,29 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G250" s="5" t="n">
+        <v>3.6e-05</v>
+      </c>
+      <c r="H250" s="5" t="n">
+        <v>5.2e-05</v>
+      </c>
+      <c r="I250" s="5" t="n">
+        <v>0.000367</v>
+      </c>
+      <c r="J250" s="5" t="n">
+        <v>0.000368</v>
+      </c>
+      <c r="K250" s="5" t="n">
+        <v>0.000816</v>
       </c>
       <c r="L250" s="5" t="n">
-        <v>-0.04643</v>
-      </c>
-      <c r="M250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N250" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.0005</v>
+      </c>
+      <c r="M250" s="5" t="n">
+        <v>0.000487</v>
+      </c>
+      <c r="N250" s="5" t="n">
+        <v>0.000468</v>
       </c>
       <c r="O250" t="inlineStr">
         <is>
@@ -30104,15 +30146,19 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>OTHER ITEMS total</t>
-        </is>
-      </c>
-      <c r="D251" t="inlineStr"/>
+          <t>Management fees (Note 9) $</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E251" t="inlineStr">
         <is>
           <t>-</t>
@@ -30128,29 +30174,25 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H251" s="5" t="n">
+        <v>0.166613</v>
+      </c>
+      <c r="I251" s="5" t="n">
+        <v>0.06</v>
       </c>
       <c r="J251" s="5" t="n">
-        <v>-0.528793</v>
-      </c>
-      <c r="K251" s="5" t="n">
-        <v>-0.370784</v>
+        <v>0.06</v>
+      </c>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L251" s="5" t="n">
-        <v>-0.04643</v>
-      </c>
-      <c r="M251" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.06</v>
+      </c>
+      <c r="M251" s="5" t="n">
+        <v>0.06</v>
       </c>
       <c r="N251" t="inlineStr">
         <is>
@@ -30191,17 +30233,17 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>COMPREHENSIVE LOSS FOR THE YEAR $</t>
+          <t>Professional and consulting fees (Note 9)</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -30225,19 +30267,19 @@
         </is>
       </c>
       <c r="I252" s="5" t="n">
-        <v>-0.811065</v>
+        <v>0.176791</v>
       </c>
       <c r="J252" s="5" t="n">
-        <v>-0.74854</v>
+        <v>0.056886</v>
       </c>
       <c r="K252" s="5" t="n">
-        <v>-0.845966</v>
+        <v>0.09901699999999999</v>
       </c>
       <c r="L252" s="5" t="n">
-        <v>-0.242169</v>
+        <v>0.077676</v>
       </c>
       <c r="M252" s="5" t="n">
-        <v>-0.195726</v>
+        <v>0.047977</v>
       </c>
       <c r="N252" t="inlineStr">
         <is>
@@ -30278,19 +30320,15 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>LOSS PER SHARE – BASIC AND DILUTED $</t>
-        </is>
-      </c>
-      <c r="D253" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Exploration and evaluation costs (Note 6)</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
       <c r="E253" t="inlineStr">
         <is>
           <t>-</t>
@@ -30312,19 +30350,19 @@
         </is>
       </c>
       <c r="I253" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.335639</v>
       </c>
       <c r="J253" s="5" t="n">
-        <v>-2e-08</v>
+        <v>-0.000106</v>
       </c>
       <c r="K253" s="5" t="n">
-        <v>-2e-08</v>
+        <v>0.0277</v>
       </c>
       <c r="L253" s="5" t="n">
-        <v>0</v>
+        <v>0.018954</v>
       </c>
       <c r="M253" s="5" t="n">
-        <v>0</v>
+        <v>0.03503</v>
       </c>
       <c r="N253" t="inlineStr">
         <is>
@@ -30370,12 +30408,12 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Professional and consulting fees (Note 9) $</t>
+          <t>LOSS FROM OPERATIONS</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -30403,21 +30441,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J254" s="5" t="n">
+        <v>-0.219747</v>
       </c>
       <c r="K254" s="5" t="n">
-        <v>0.09901699999999999</v>
+        <v>-0.475182</v>
       </c>
       <c r="L254" s="5" t="n">
-        <v>0.077676</v>
-      </c>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.195739</v>
+      </c>
+      <c r="M254" s="5" t="n">
+        <v>-0.195726</v>
       </c>
       <c r="N254" t="inlineStr">
         <is>
@@ -30458,19 +30492,15 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Management fees (Note 9)</t>
-        </is>
-      </c>
-      <c r="D255" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Loss on debt settlement (Note 7)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr"/>
       <c r="E255" t="inlineStr">
         <is>
           <t>-</t>
@@ -30486,20 +30516,28 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H255" s="5" t="n">
-        <v>0.166613</v>
-      </c>
-      <c r="I255" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="J255" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="K255" s="5" t="n">
-        <v>0.06</v>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="L255" s="5" t="n">
-        <v>0.06</v>
+        <v>-0.04643</v>
       </c>
       <c r="M255" t="inlineStr">
         <is>
@@ -30545,12 +30583,12 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 8)</t>
+          <t>OTHER ITEMS total</t>
         </is>
       </c>
       <c r="D256" t="inlineStr"/>
@@ -30569,22 +30607,24 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H256" s="5" t="n">
-        <v>0.031125</v>
-      </c>
-      <c r="I256" s="5" t="n">
-        <v>0.119613</v>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J256" s="5" t="n">
-        <v>0.047066</v>
+        <v>-0.528793</v>
       </c>
       <c r="K256" s="5" t="n">
-        <v>0.007764</v>
-      </c>
-      <c r="L256" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.370784</v>
+      </c>
+      <c r="L256" s="5" t="n">
+        <v>-0.04643</v>
       </c>
       <c r="M256" t="inlineStr">
         <is>
@@ -30635,10 +30675,14 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Write-off of Northumberland (Note 10)</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr"/>
+          <t>COMPREHENSIVE LOSS FOR THE YEAR $</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E257" t="inlineStr">
         <is>
           <t>-</t>
@@ -30659,28 +30703,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I257" s="5" t="n">
+        <v>-0.811065</v>
+      </c>
+      <c r="J257" s="5" t="n">
+        <v>-0.74854</v>
       </c>
       <c r="K257" s="5" t="n">
-        <v>-0.356237</v>
-      </c>
-      <c r="L257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.845966</v>
+      </c>
+      <c r="L257" s="5" t="n">
+        <v>-0.242169</v>
+      </c>
+      <c r="M257" s="5" t="n">
+        <v>-0.195726</v>
       </c>
       <c r="N257" t="inlineStr">
         <is>
@@ -30726,10 +30762,14 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Loss on debt settlement (Notes 7 and 9)</t>
-        </is>
-      </c>
-      <c r="D258" t="inlineStr"/>
+          <t>LOSS PER SHARE – BASIC AND DILUTED $</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E258" t="inlineStr">
         <is>
           <t>-</t>
@@ -30750,26 +30790,20 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I258" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="J258" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="K258" s="5" t="n">
-        <v>-0.014547</v>
+        <v>-2e-08</v>
       </c>
       <c r="L258" s="5" t="n">
-        <v>-0.04643</v>
-      </c>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="M258" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="N258" t="inlineStr">
         <is>
@@ -30815,10 +30849,14 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Property investigation costs $</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr"/>
+          <t>Professional and consulting fees (Note 9) $</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
@@ -30850,12 +30888,10 @@
         </is>
       </c>
       <c r="K259" s="5" t="n">
-        <v>0.173911</v>
-      </c>
-      <c r="L259" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.09901699999999999</v>
+      </c>
+      <c r="L259" s="5" t="n">
+        <v>0.077676</v>
       </c>
       <c r="M259" t="inlineStr">
         <is>
@@ -30906,12 +30942,12 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Management fees (Note 9)</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
@@ -30930,23 +30966,19 @@
         </is>
       </c>
       <c r="H260" s="5" t="n">
-        <v>0.000174</v>
-      </c>
-      <c r="I260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.166613</v>
+      </c>
+      <c r="I260" s="5" t="n">
+        <v>0.06</v>
       </c>
       <c r="J260" s="5" t="n">
-        <v>0.000463</v>
+        <v>0.06</v>
       </c>
       <c r="K260" s="5" t="n">
-        <v>0.000363</v>
-      </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.06</v>
+      </c>
+      <c r="L260" s="5" t="n">
+        <v>0.06</v>
       </c>
       <c r="M260" t="inlineStr">
         <is>
@@ -30992,12 +31024,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Write-off of mineral properties (Note 6)</t>
+          <t>Share-based payments (Note 8)</t>
         </is>
       </c>
       <c r="D261" t="inlineStr"/>
@@ -31016,23 +31048,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H261" s="5" t="n">
+        <v>0.031125</v>
+      </c>
+      <c r="I261" s="5" t="n">
+        <v>0.119613</v>
       </c>
       <c r="J261" s="5" t="n">
-        <v>-0.53225</v>
-      </c>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.047066</v>
+      </c>
+      <c r="K261" s="5" t="n">
+        <v>0.007764</v>
       </c>
       <c r="L261" t="inlineStr">
         <is>
@@ -31088,7 +31114,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Loss on debt settlement (Note 9)</t>
+          <t>Write-off of Northumberland (Note 10)</t>
         </is>
       </c>
       <c r="D262" t="inlineStr"/>
@@ -31123,7 +31149,7 @@
         </is>
       </c>
       <c r="K262" s="5" t="n">
-        <v>-0.014547</v>
+        <v>-0.356237</v>
       </c>
       <c r="L262" t="inlineStr">
         <is>
@@ -31179,7 +31205,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Gain on debt settlement</t>
+          <t>Loss on debt settlement (Notes 7 and 9)</t>
         </is>
       </c>
       <c r="D263" t="inlineStr"/>
@@ -31208,18 +31234,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="J263" s="5" t="n">
-        <v>0.003457</v>
-      </c>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K263" s="5" t="n">
+        <v>-0.014547</v>
+      </c>
+      <c r="L263" s="5" t="n">
+        <v>-0.04643</v>
       </c>
       <c r="M263" t="inlineStr">
         <is>
@@ -31270,14 +31294,10 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (gain)</t>
-        </is>
-      </c>
-      <c r="D264" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Property investigation costs $</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr"/>
       <c r="E264" t="inlineStr">
         <is>
           <t>-</t>
@@ -31293,19 +31313,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H264" s="5" t="n">
-        <v>0.000174</v>
-      </c>
-      <c r="I264" s="5" t="n">
-        <v>-0.001844</v>
-      </c>
-      <c r="J264" s="5" t="n">
-        <v>0.000463</v>
-      </c>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K264" s="5" t="n">
+        <v>0.173911</v>
       </c>
       <c r="L264" t="inlineStr">
         <is>
@@ -31361,12 +31385,12 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>LOSS FROM OPERATIONS $</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>OperatingIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -31384,21 +31408,19 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I265" s="5" t="n">
-        <v>-0.811065</v>
+      <c r="H265" s="5" t="n">
+        <v>0.000174</v>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J265" s="5" t="n">
-        <v>-0.219747</v>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000463</v>
+      </c>
+      <c r="K265" s="5" t="n">
+        <v>0.000363</v>
       </c>
       <c r="L265" t="inlineStr">
         <is>
@@ -31449,12 +31471,12 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Exploration and evaluation costs $</t>
+          <t>Write-off of mineral properties (Note 6)</t>
         </is>
       </c>
       <c r="D266" t="inlineStr"/>
@@ -31473,16 +31495,18 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H266" s="5" t="n">
-        <v>0.016602</v>
-      </c>
-      <c r="I266" s="5" t="n">
-        <v>0.335639</v>
-      </c>
-      <c r="J266" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J266" s="5" t="n">
+        <v>-0.53225</v>
       </c>
       <c r="K266" t="inlineStr">
         <is>
@@ -31538,19 +31562,15 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Professional and consulting fees</t>
-        </is>
-      </c>
-      <c r="D267" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Loss on debt settlement (Note 9)</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr"/>
       <c r="E267" t="inlineStr">
         <is>
           <t>-</t>
@@ -31566,21 +31586,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H267" s="5" t="n">
-        <v>0.067426</v>
-      </c>
-      <c r="I267" s="5" t="n">
-        <v>0.176791</v>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J267" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K267" s="5" t="n">
+        <v>-0.014547</v>
       </c>
       <c r="L267" t="inlineStr">
         <is>
@@ -31631,38 +31653,42 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>NET LOSS AND COMPREHENSIVE LOSS $</t>
-        </is>
-      </c>
-      <c r="D268" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E268" s="5" t="n">
-        <v>-0.040102</v>
-      </c>
-      <c r="F268" s="5" t="n">
-        <v>-0.113722</v>
-      </c>
-      <c r="G268" s="5" t="n">
-        <v>-0.040102</v>
-      </c>
-      <c r="H268" s="5" t="n">
-        <v>-0.362402</v>
-      </c>
-      <c r="I268" s="5" t="n">
-        <v>-0.811065</v>
-      </c>
-      <c r="J268" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Gain on debt settlement</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J268" s="5" t="n">
+        <v>0.003457</v>
       </c>
       <c r="K268" t="inlineStr">
         <is>
@@ -31723,33 +31749,37 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>LOSS PER SHARE – BASIC AND DILUTED $</t>
+          <t>Foreign exchange loss (gain)</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E269" s="5" t="n">
-        <v>-1e-08</v>
-      </c>
-      <c r="F269" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="G269" s="5" t="n">
-        <v>0</v>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H269" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.000174</v>
       </c>
       <c r="I269" s="5" t="n">
-        <v>-2e-08</v>
-      </c>
-      <c r="J269" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.001844</v>
+      </c>
+      <c r="J269" s="5" t="n">
+        <v>0.000463</v>
       </c>
       <c r="K269" t="inlineStr">
         <is>
@@ -31810,12 +31840,12 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Professional and consulting fees (Note 14)</t>
+          <t>LOSS FROM OPERATIONS $</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>OperatingIncome</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
@@ -31828,21 +31858,21 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G270" s="5" t="n">
-        <v>0.016605</v>
-      </c>
-      <c r="H270" s="5" t="n">
-        <v>0.067426</v>
-      </c>
-      <c r="I270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J270" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I270" s="5" t="n">
+        <v>-0.811065</v>
+      </c>
+      <c r="J270" s="5" t="n">
+        <v>-0.219747</v>
       </c>
       <c r="K270" t="inlineStr">
         <is>
@@ -31903,7 +31933,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Exploration and evaluation costs</t>
+          <t>Exploration and evaluation costs $</t>
         </is>
       </c>
       <c r="D271" t="inlineStr"/>
@@ -31925,10 +31955,8 @@
       <c r="H271" s="5" t="n">
         <v>0.016602</v>
       </c>
-      <c r="I271" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I271" s="5" t="n">
+        <v>0.335639</v>
       </c>
       <c r="J271" t="inlineStr">
         <is>
@@ -31987,33 +32015,41 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B272" t="inlineStr"/>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>2011 TO MARCH</t>
-        </is>
-      </c>
-      <c r="D272" t="inlineStr"/>
-      <c r="E272" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="F272" s="5" t="n">
-        <v>0.002012</v>
+          <t>Professional and consulting fees</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I272" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H272" s="5" t="n">
+        <v>0.067426</v>
+      </c>
+      <c r="I272" s="5" t="n">
+        <v>0.176791</v>
       </c>
       <c r="J272" t="inlineStr">
         <is>
@@ -32079,30 +32115,28 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Accounting $</t>
-        </is>
-      </c>
-      <c r="D273" t="inlineStr"/>
+          <t>NET LOSS AND COMPREHENSIVE LOSS $</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E273" s="5" t="n">
-        <v>0.008272</v>
+        <v>-0.040102</v>
       </c>
       <c r="F273" s="5" t="n">
-        <v>0.017058</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I273" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.113722</v>
+      </c>
+      <c r="G273" s="5" t="n">
+        <v>-0.040102</v>
+      </c>
+      <c r="H273" s="5" t="n">
+        <v>-0.362402</v>
+      </c>
+      <c r="I273" s="5" t="n">
+        <v>-0.811065</v>
       </c>
       <c r="J273" t="inlineStr">
         <is>
@@ -32168,34 +32202,28 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Bank charges</t>
+          <t>LOSS PER SHARE – BASIC AND DILUTED $</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E274" s="5" t="n">
-        <v>3.6e-05</v>
+        <v>-1e-08</v>
       </c>
       <c r="F274" s="5" t="n">
-        <v>0.000125</v>
-      </c>
-      <c r="G274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I274" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-2e-08</v>
+      </c>
+      <c r="G274" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H274" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="I274" s="5" t="n">
+        <v>-2e-08</v>
       </c>
       <c r="J274" t="inlineStr">
         <is>
@@ -32261,29 +32289,29 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Legal</t>
+          <t>Professional and consulting fees (Note 14)</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E275" s="5" t="n">
-        <v>0.008333</v>
-      </c>
-      <c r="F275" s="5" t="n">
-        <v>0.004105</v>
-      </c>
-      <c r="G275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H275" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G275" s="5" t="n">
+        <v>0.016605</v>
+      </c>
+      <c r="H275" s="5" t="n">
+        <v>0.067426</v>
       </c>
       <c r="I275" t="inlineStr">
         <is>
@@ -32354,7 +32382,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Share-based payments (Note 5)</t>
+          <t>Exploration and evaluation costs</t>
         </is>
       </c>
       <c r="D276" t="inlineStr"/>
@@ -32363,70 +32391,802 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F276" s="5" t="n">
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H276" s="5" t="n">
+        <v>0.016602</v>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr"/>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2011 TO MARCH</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="F277" s="5" t="n">
+        <v>0.002012</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Accounting $</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" s="5" t="n">
+        <v>0.008272</v>
+      </c>
+      <c r="F278" s="5" t="n">
+        <v>0.017058</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Bank charges</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E279" s="5" t="n">
+        <v>3.6e-05</v>
+      </c>
+      <c r="F279" s="5" t="n">
+        <v>0.000125</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Legal</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E280" s="5" t="n">
+        <v>0.008333</v>
+      </c>
+      <c r="F280" s="5" t="n">
+        <v>0.004105</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Share-based payments (Note 5)</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F281" s="5" t="n">
         <v>0.059737</v>
       </c>
-      <c r="G276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="R276" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="S276" t="inlineStr">
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Advertising and promotion</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F282" s="5" t="n">
+        <v>0.00058</v>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Share-based payments (Notes 5 and 6)</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F283" s="5" t="n">
+        <v>0.059737</v>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER OF COMMON SHARES OUTSTANDING</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F284" s="5" t="n">
+        <v>4.654108</v>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R284" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S284" t="inlineStr">
         <is>
           <t>-</t>
         </is>
